--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T14:56:23+00:00</t>
+    <t>2025-01-06T16:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="134">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -315,6 +315,10 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
   </si>
   <si>
     <t>Informant.typeId.nullFlavor</t>
@@ -1277,7 +1281,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1285,10 +1289,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1386,17 +1390,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1414,11 +1418,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1469,7 +1473,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1489,17 +1493,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1517,11 +1521,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1572,7 +1576,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1592,17 +1596,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1620,11 +1624,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1633,7 +1637,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1675,7 +1679,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1695,17 +1699,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1723,11 +1727,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1778,7 +1782,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1798,10 +1802,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1828,7 +1832,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1879,7 +1883,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1899,10 +1903,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1936,7 +1940,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -1958,7 +1962,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -1976,7 +1980,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -1996,10 +2000,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2033,7 +2037,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2055,7 +2059,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2073,7 +2077,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2093,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2119,7 +2123,7 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -2172,7 +2176,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2192,10 +2196,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2218,7 +2222,7 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -2271,7 +2275,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="136">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -421,11 +421,20 @@
 </t>
   </si>
   <si>
+    <t>Professionnel / Structure / Patient/usager ayant fourni des informations relatives au document.</t>
+  </si>
+  <si>
     <t>Informant.relatedEntity</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/RelatedEntity {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-related-entity}
 </t>
+  </si>
+  <si>
+    <t>Informateur non professionnel ayant fourni des informations relatives au document. 
+Ou : Personne de confiance désignée par le patient/usager.
+Ou : Personne à prévenir en cas d’urgence. 
+Ou : Aidant du patient/usager. ou : Personne aidée</t>
   </si>
 </sst>
 </file>
@@ -2125,7 +2134,9 @@
       <c r="K14" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L14" s="2"/>
+      <c r="L14" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2196,10 +2207,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2222,9 +2233,11 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L15" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2275,7 +2288,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Informateur / personne de confiance / personne à prévenir en cas d’urgence / aidant / personne aidée.</t>
+    <t>L'élément de l'en-tête du CDA informant permet d'identifier un informateur, une personne de confiance, une personne à prévenir en cas d’urgence, un aidant ou une personne aidée.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
